--- a/pensum/ol11/OL11_Klasseoppgaver_v5.xlsx
+++ b/pensum/ol11/OL11_Klasseoppgaver_v5.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="163">
   <si>
     <t xml:space="preserve">Klasseoppgaver til Organisasjon og ledelse kapittel 11: Hva er en organisasjon? (V5)</t>
   </si>
@@ -161,6 +161,12 @@
     <t xml:space="preserve">a)  Tegn organisasjonskartet ut fra tabellen. Hvor mange personer har Kari, som daglig leder, direkte under seg?</t>
   </si>
   <si>
+    <t xml:space="preserve">Formel og begrep</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linjeorganisasjon: hver ansatt har én overordnet, og kartet viser hvem som svarer til hvem (figur 11.1; kap. 14).</t>
+  </si>
+  <si>
     <t xml:space="preserve">b)  Gå gjennom fire av bokas seks kjennetegn på en formell organisasjon. Hvilke er helt på plass hos Nordlys? Svar ja eller nei for hvert, og begrunn med tabellen.</t>
   </si>
   <si>
@@ -185,6 +191,24 @@
     <t xml:space="preserve">e)  Kari vil rette opp etter de tre hendelsene, uten å ansette noen. Foreslå to tiltak hun bør gjøre først, si hvilket kjennetegn hvert tiltak gir innhold, og hva det koster.</t>
   </si>
   <si>
+    <t xml:space="preserve">De seks kjennetegnene (Organisasjon og ledelse 11.1); i kap. 14 sier Fayol at ansvar og myndighet må stå i forhold til hverandre.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hint, hvis du står fast</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tegn kartet først</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sett Kari øverst. Hvem har en leder mellom seg og henne, og hvem har det ikke? Tell bare de som står rett under henne (slide 11).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hvem hadde fått oppgaven?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spør for hver hendelse: hvem hadde fått oppgaven på forhånd, skriftlig? Gå så gjennom de seks kjennetegnene (slide 10).</t>
+  </si>
+  <si>
     <t xml:space="preserve">Kilde: Hjertnes, F.: Markedsføring, organisasjon og ledelse for LØM-emnet, kap. 11.1 (formelle og uformelle organisasjoner, figur 11.1). Nordlys Elektro AS er en konstruert casebedrift.</t>
   </si>
   <si>
@@ -248,6 +272,9 @@
     <t xml:space="preserve">a)  Med tre personer er det 3 mulige forbindelser. Hvor mange blir det når Fjell er fem personer? Bruk n × (n − 1) / 2.</t>
   </si>
   <si>
+    <t xml:space="preserve">n × (n − 1) / 2 er en telleregel for antall mulige forbindelser mellom to personer, ikke en formel i boka. Den brukes til å vise hvorfor arbeidsdeling og samordning må bestemmes (definisjonen i kap. 12).</t>
+  </si>
+  <si>
     <t xml:space="preserve">b)  Hvilke av disse trekkene ved Fjell er formelle, etter bokas kjennetegn? Svar ja eller nei for hvert, og si hvilket kjennetegn de formelle hører til.</t>
   </si>
   <si>
@@ -275,6 +302,21 @@
     <t xml:space="preserve">e)  Lærlingen og den nye montøren begynner neste år. Hvilke to ting bør Mona skrive ned før de begynner? Begrunn med bokas kjennetegn, og si hva hun bør beholde av det uformelle.</t>
   </si>
   <si>
+    <t xml:space="preserve">De seks kjennetegnene (Organisasjon og ledelse 11.1), definisjonen med arbeidsdeling og samordning (kap. 12) og formelle og uformelle trekk (12.4).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Telleregelen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ganger antall personer med én mindre, og del på 2, fordi samtalen mellom to bare telles én gang (slide 7).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skrevet ned eller avtalt muntlig?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Det formelle er det som står i avtaler, mål og instrukser. Det uformelle er det som bare skjer. Størrelse er ikke et kjennetegn (slide 9–10).</t>
+  </si>
+  <si>
     <t xml:space="preserve">Kilde: Hjertnes, F.: Markedsføring, organisasjon og ledelse for LØM-emnet, kap. 11.1; definisjonen i kap. 12 (innledningen) og formelle og uformelle trekk i 12.4. Fjell Elektro AS er en konstruert casebedrift.</t>
   </si>
   <si>
@@ -362,6 +404,21 @@
     <t xml:space="preserve">e)  Foreslå ett tiltak per perspektiv som kan gjøres uten å ansette noen. Ranger dem etter hva de koster, og si hvilket som virker allerede samme uke.</t>
   </si>
   <si>
+    <t xml:space="preserve">De tre perspektivene (Organisasjon og ledelse 11.2–11.4).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rår Nordlys over det?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill mellom det leverandøren bestemmer og det Nordlys bestemmer selv. Når de bestiller, er deres eget valg (slide 28).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rutine, norm eller omgivelser?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maskin ser etter rutinen. Fellesskapet ser etter normen. Åpent system ser etter det bedriften ikke rår over (slide 29).</t>
+  </si>
+  <si>
     <t xml:space="preserve">Kilde: Hjertnes, F.: Markedsføring, organisasjon og ledelse for LØM-emnet, kap. 11.2–11.4. Nordlys Elektro AS er en konstruert casebedrift.</t>
   </si>
   <si>
@@ -438,6 +495,21 @@
   </si>
   <si>
     <t xml:space="preserve">e)  Mona har én dag til ledelse neste uke. Foreslå ett tiltak per perspektiv, og si hvilket hun bør gjøre først og hvorfor.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">De tre perspektivene (Organisasjon og ledelse 11.2–11.4) og Hawthorne (15.1).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ute eller inne?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Konkurrenter, leverandører og kunder er omgivelsene. Det montørene sier og gjør, skjer inne i Fjell (slide 28).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hawthorne og sjekklista</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hawthorne handlet om oppmerksomhet, ikke om lys (slide 26). Sjekklista er en rutine, og rutiner er maskinperspektivets virkemiddel (slide 25).</t>
   </si>
   <si>
     <t xml:space="preserve">Kilde: Hjertnes, F.: Markedsføring, organisasjon og ledelse for LØM-emnet, kap. 11.2–11.4; Hawthorne i 15.1. Fjell Elektro AS er en konstruert casebedrift.</t>
@@ -451,7 +523,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="#,##0.##;\−#,##0.##;\0"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -518,8 +590,30 @@
       <family val="0"/>
       <charset val="1"/>
     </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FF2F4A6D"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -535,13 +629,31 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF4F6FA"/>
-        <bgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFEEF2F8"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
         <bgColor rgb="FFFFFF00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEF2F8"/>
+        <bgColor rgb="FFF4F6FA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB8954A"/>
+        <bgColor rgb="FF808080"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBF6EA"/>
+        <bgColor rgb="FFF4F6FA"/>
       </patternFill>
     </fill>
   </fills>
@@ -594,7 +706,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="25">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -663,11 +775,31 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -704,8 +836,8 @@
       <rgbColor rgb="FF808080"/>
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFF4F6FA"/>
-      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFFBF6EA"/>
+      <rgbColor rgb="FFEEF2F8"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
       <rgbColor rgb="FF0066CC"/>
@@ -719,7 +851,7 @@
       <rgbColor rgb="FF008080"/>
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFF4F6FA"/>
       <rgbColor rgb="FFCCFFCC"/>
       <rgbColor rgb="FFFFFF99"/>
       <rgbColor rgb="FF99CCFF"/>
@@ -733,7 +865,7 @@
       <rgbColor rgb="FFFF9900"/>
       <rgbColor rgb="FFFF6600"/>
       <rgbColor rgb="FF5E6670"/>
-      <rgbColor rgb="FF969696"/>
+      <rgbColor rgb="FFB8954A"/>
       <rgbColor rgb="FF003366"/>
       <rgbColor rgb="FF339966"/>
       <rgbColor rgb="FF003300"/>
@@ -1036,7 +1168,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:G40"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
@@ -1181,30 +1313,20 @@
         <v/>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="7" t="s">
+    <row r="19" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="B19" s="7"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7"/>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="7" t="s">
+      <c r="B19" s="18" t="s">
         <v>46</v>
       </c>
-      <c r="B20" s="7"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="7"/>
-      <c r="F20" s="17"/>
-      <c r="G20" s="16" t="str">
-        <f aca="false">IF(F20="","",IF(UPPER(TRIM(F20))="JA","Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C19" s="18"/>
+      <c r="D19" s="18"/>
+      <c r="E19" s="18"/>
+      <c r="F19" s="18"/>
+      <c r="G19" s="18"/>
+    </row>
+    <row r="21" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="7" t="s">
         <v>47</v>
       </c>
@@ -1212,11 +1334,6 @@
       <c r="C21" s="7"/>
       <c r="D21" s="7"/>
       <c r="E21" s="7"/>
-      <c r="F21" s="17"/>
-      <c r="G21" s="16" t="str">
-        <f aca="false">IF(F21="","",IF(UPPER(TRIM(F21))="NEI","Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="7" t="s">
@@ -1226,9 +1343,9 @@
       <c r="C22" s="7"/>
       <c r="D22" s="7"/>
       <c r="E22" s="7"/>
-      <c r="F22" s="17"/>
+      <c r="F22" s="19"/>
       <c r="G22" s="16" t="str">
-        <f aca="false">IF(F22="","",IF(UPPER(TRIM(F22))="NEI","Riktig","Prøv igjen"))</f>
+        <f aca="false">IF(F22="","",IF(UPPER(TRIM(F22))="JA","Riktig","Prøv igjen"))</f>
         <v/>
       </c>
     </row>
@@ -1240,13 +1357,13 @@
       <c r="C23" s="7"/>
       <c r="D23" s="7"/>
       <c r="E23" s="7"/>
-      <c r="F23" s="17"/>
+      <c r="F23" s="19"/>
       <c r="G23" s="16" t="str">
         <f aca="false">IF(F23="","",IF(UPPER(TRIM(F23))="NEI","Riktig","Prøv igjen"))</f>
         <v/>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="7" t="s">
         <v>50</v>
       </c>
@@ -1254,13 +1371,13 @@
       <c r="C24" s="7"/>
       <c r="D24" s="7"/>
       <c r="E24" s="7"/>
-      <c r="F24" s="17"/>
+      <c r="F24" s="19"/>
       <c r="G24" s="16" t="str">
-        <f aca="false">IF(F24="","",IF(UPPER(TRIM(F24))="B","Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <f aca="false">IF(F24="","",IF(UPPER(TRIM(F24))="NEI","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="7" t="s">
         <v>51</v>
       </c>
@@ -1268,13 +1385,13 @@
       <c r="C25" s="7"/>
       <c r="D25" s="7"/>
       <c r="E25" s="7"/>
-      <c r="F25" s="17"/>
+      <c r="F25" s="19"/>
       <c r="G25" s="16" t="str">
-        <f aca="false">IF(F25="","",IF(UPPER(TRIM(F25))="B","Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <f aca="false">IF(F25="","",IF(UPPER(TRIM(F25))="NEI","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="7" t="s">
         <v>52</v>
       </c>
@@ -1282,74 +1399,157 @@
       <c r="C26" s="7"/>
       <c r="D26" s="7"/>
       <c r="E26" s="7"/>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="18"/>
-      <c r="B27" s="18"/>
-      <c r="C27" s="18"/>
-      <c r="D27" s="18"/>
-      <c r="E27" s="18"/>
-      <c r="F27" s="18"/>
-      <c r="G27" s="18"/>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="18"/>
-      <c r="B28" s="18"/>
-      <c r="C28" s="18"/>
-      <c r="D28" s="18"/>
-      <c r="E28" s="18"/>
-      <c r="F28" s="18"/>
-      <c r="G28" s="18"/>
+      <c r="F26" s="19"/>
+      <c r="G26" s="16" t="str">
+        <f aca="false">IF(F26="","",IF(UPPER(TRIM(F26))="B","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="B27" s="7"/>
+      <c r="C27" s="7"/>
+      <c r="D27" s="7"/>
+      <c r="E27" s="7"/>
+      <c r="F27" s="19"/>
+      <c r="G27" s="16" t="str">
+        <f aca="false">IF(F27="","",IF(UPPER(TRIM(F27))="B","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="B28" s="7"/>
+      <c r="C28" s="7"/>
+      <c r="D28" s="7"/>
+      <c r="E28" s="7"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="18"/>
-      <c r="B29" s="18"/>
-      <c r="C29" s="18"/>
-      <c r="D29" s="18"/>
-      <c r="E29" s="18"/>
-      <c r="F29" s="18"/>
-      <c r="G29" s="18"/>
-    </row>
-    <row r="31" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="B31" s="6"/>
-      <c r="C31" s="6"/>
-      <c r="D31" s="6"/>
-      <c r="E31" s="6"/>
-      <c r="F31" s="6"/>
-      <c r="G31" s="6"/>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="B32" s="6"/>
-      <c r="C32" s="6"/>
-      <c r="D32" s="6"/>
-      <c r="E32" s="6"/>
-      <c r="F32" s="6"/>
-      <c r="G32" s="6"/>
+      <c r="A29" s="20"/>
+      <c r="B29" s="20"/>
+      <c r="C29" s="20"/>
+      <c r="D29" s="20"/>
+      <c r="E29" s="20"/>
+      <c r="F29" s="20"/>
+      <c r="G29" s="20"/>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="20"/>
+      <c r="B30" s="20"/>
+      <c r="C30" s="20"/>
+      <c r="D30" s="20"/>
+      <c r="E30" s="20"/>
+      <c r="F30" s="20"/>
+      <c r="G30" s="20"/>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="20"/>
+      <c r="B31" s="20"/>
+      <c r="C31" s="20"/>
+      <c r="D31" s="20"/>
+      <c r="E31" s="20"/>
+      <c r="F31" s="20"/>
+      <c r="G31" s="20"/>
+    </row>
+    <row r="32" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="B32" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="C32" s="18"/>
+      <c r="D32" s="18"/>
+      <c r="E32" s="18"/>
+      <c r="F32" s="18"/>
+      <c r="G32" s="18"/>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="21" t="s">
+        <v>56</v>
+      </c>
+      <c r="B35" s="21"/>
+      <c r="C35" s="21"/>
+      <c r="D35" s="21"/>
+      <c r="E35" s="21"/>
+      <c r="F35" s="21"/>
+      <c r="G35" s="21"/>
+    </row>
+    <row r="36" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="22" t="s">
+        <v>57</v>
+      </c>
+      <c r="B36" s="23" t="s">
+        <v>58</v>
+      </c>
+      <c r="C36" s="23"/>
+      <c r="D36" s="23"/>
+      <c r="E36" s="23"/>
+      <c r="F36" s="23"/>
+      <c r="G36" s="23"/>
+    </row>
+    <row r="37" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="B37" s="23" t="s">
+        <v>60</v>
+      </c>
+      <c r="C37" s="23"/>
+      <c r="D37" s="23"/>
+      <c r="E37" s="23"/>
+      <c r="F37" s="23"/>
+      <c r="G37" s="23"/>
+    </row>
+    <row r="39" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="B39" s="6"/>
+      <c r="C39" s="6"/>
+      <c r="D39" s="6"/>
+      <c r="E39" s="6"/>
+      <c r="F39" s="6"/>
+      <c r="G39" s="6"/>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="B40" s="6"/>
+      <c r="C40" s="6"/>
+      <c r="D40" s="6"/>
+      <c r="E40" s="6"/>
+      <c r="F40" s="6"/>
+      <c r="G40" s="6"/>
     </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="21">
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="A15:G15"/>
     <mergeCell ref="A17:E17"/>
     <mergeCell ref="A18:E18"/>
-    <mergeCell ref="A19:E19"/>
-    <mergeCell ref="A20:E20"/>
+    <mergeCell ref="B19:G19"/>
     <mergeCell ref="A21:E21"/>
     <mergeCell ref="A22:E22"/>
     <mergeCell ref="A23:E23"/>
     <mergeCell ref="A24:E24"/>
     <mergeCell ref="A25:E25"/>
     <mergeCell ref="A26:E26"/>
-    <mergeCell ref="A27:G29"/>
-    <mergeCell ref="A31:G31"/>
-    <mergeCell ref="A32:G32"/>
+    <mergeCell ref="A27:E27"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="A29:G31"/>
+    <mergeCell ref="B32:G32"/>
+    <mergeCell ref="A35:G35"/>
+    <mergeCell ref="B36:G36"/>
+    <mergeCell ref="B37:G37"/>
+    <mergeCell ref="A39:G39"/>
+    <mergeCell ref="A40:G40"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -1366,7 +1566,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:G40"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
@@ -1377,7 +1577,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1387,7 +1587,7 @@
     </row>
     <row r="4" customFormat="false" ht="78.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
@@ -1398,7 +1598,7 @@
     </row>
     <row r="5" customFormat="false" ht="78.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
@@ -1409,10 +1609,10 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="C7" s="14"/>
       <c r="D7" s="14"/>
@@ -1421,11 +1621,11 @@
       <c r="G7" s="14"/>
     </row>
     <row r="8" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="19" t="s">
-        <v>60</v>
+      <c r="A8" s="24" t="s">
+        <v>68</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="C8" s="7"/>
       <c r="D8" s="7"/>
@@ -1434,11 +1634,11 @@
       <c r="G8" s="7"/>
     </row>
     <row r="9" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="19" t="s">
-        <v>62</v>
+      <c r="A9" s="24" t="s">
+        <v>70</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
@@ -1447,11 +1647,11 @@
       <c r="G9" s="7"/>
     </row>
     <row r="10" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="19" t="s">
-        <v>64</v>
+      <c r="A10" s="24" t="s">
+        <v>72</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="C10" s="7"/>
       <c r="D10" s="7"/>
@@ -1460,11 +1660,11 @@
       <c r="G10" s="7"/>
     </row>
     <row r="11" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="19" t="s">
+      <c r="A11" s="24" t="s">
         <v>38</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="C11" s="7"/>
       <c r="D11" s="7"/>
@@ -1473,11 +1673,11 @@
       <c r="G11" s="7"/>
     </row>
     <row r="12" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="19" t="s">
-        <v>67</v>
+      <c r="A12" s="24" t="s">
+        <v>75</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="C12" s="7"/>
       <c r="D12" s="7"/>
@@ -1486,11 +1686,11 @@
       <c r="G12" s="7"/>
     </row>
     <row r="13" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="19" t="s">
-        <v>69</v>
+      <c r="A13" s="24" t="s">
+        <v>77</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="C13" s="7"/>
       <c r="D13" s="7"/>
@@ -1499,11 +1699,11 @@
       <c r="G13" s="7"/>
     </row>
     <row r="14" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="19" t="s">
-        <v>71</v>
+      <c r="A14" s="24" t="s">
+        <v>79</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="C14" s="7"/>
       <c r="D14" s="7"/>
@@ -1528,7 +1728,7 @@
     </row>
     <row r="17" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="7" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="B17" s="7"/>
       <c r="C17" s="7"/>
@@ -1540,66 +1740,51 @@
         <v/>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="B18" s="7"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="7"/>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="B19" s="7"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="17"/>
-      <c r="G19" s="16" t="str">
-        <f aca="false">IF(F19="","",IF(UPPER(TRIM(F19))="JA","Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="B18" s="18" t="s">
+        <v>82</v>
+      </c>
+      <c r="C18" s="18"/>
+      <c r="D18" s="18"/>
+      <c r="E18" s="18"/>
+      <c r="F18" s="18"/>
+      <c r="G18" s="18"/>
+    </row>
+    <row r="20" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="7" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="B20" s="7"/>
       <c r="C20" s="7"/>
       <c r="D20" s="7"/>
       <c r="E20" s="7"/>
-      <c r="F20" s="17"/>
-      <c r="G20" s="16" t="str">
-        <f aca="false">IF(F20="","",IF(UPPER(TRIM(F20))="JA","Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="7" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="B21" s="7"/>
       <c r="C21" s="7"/>
       <c r="D21" s="7"/>
       <c r="E21" s="7"/>
-      <c r="F21" s="17"/>
+      <c r="F21" s="19"/>
       <c r="G21" s="16" t="str">
-        <f aca="false">IF(F21="","",IF(UPPER(TRIM(F21))="NEI","Riktig","Prøv igjen"))</f>
+        <f aca="false">IF(F21="","",IF(UPPER(TRIM(F21))="JA","Riktig","Prøv igjen"))</f>
         <v/>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="7" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="B22" s="7"/>
       <c r="C22" s="7"/>
       <c r="D22" s="7"/>
       <c r="E22" s="7"/>
-      <c r="F22" s="17"/>
+      <c r="F22" s="19"/>
       <c r="G22" s="16" t="str">
         <f aca="false">IF(F22="","",IF(UPPER(TRIM(F22))="JA","Riktig","Prøv igjen"))</f>
         <v/>
@@ -1607,106 +1792,184 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="7" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="B23" s="7"/>
       <c r="C23" s="7"/>
       <c r="D23" s="7"/>
       <c r="E23" s="7"/>
-      <c r="F23" s="17"/>
+      <c r="F23" s="19"/>
       <c r="G23" s="16" t="str">
         <f aca="false">IF(F23="","",IF(UPPER(TRIM(F23))="NEI","Riktig","Prøv igjen"))</f>
         <v/>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="7" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="B24" s="7"/>
       <c r="C24" s="7"/>
       <c r="D24" s="7"/>
       <c r="E24" s="7"/>
-      <c r="F24" s="17"/>
+      <c r="F24" s="19"/>
       <c r="G24" s="16" t="str">
-        <f aca="false">IF(F24="","",IF(UPPER(TRIM(F24))="A","Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="78.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <f aca="false">IF(F24="","",IF(UPPER(TRIM(F24))="JA","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="7" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="B25" s="7"/>
       <c r="C25" s="7"/>
       <c r="D25" s="7"/>
       <c r="E25" s="7"/>
-      <c r="F25" s="17"/>
+      <c r="F25" s="19"/>
       <c r="G25" s="16" t="str">
-        <f aca="false">IF(F25="","",IF(UPPER(TRIM(F25))="B","Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <f aca="false">IF(F25="","",IF(UPPER(TRIM(F25))="NEI","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="7" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="B26" s="7"/>
       <c r="C26" s="7"/>
       <c r="D26" s="7"/>
       <c r="E26" s="7"/>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="18"/>
-      <c r="B27" s="18"/>
-      <c r="C27" s="18"/>
-      <c r="D27" s="18"/>
-      <c r="E27" s="18"/>
-      <c r="F27" s="18"/>
-      <c r="G27" s="18"/>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="18"/>
-      <c r="B28" s="18"/>
-      <c r="C28" s="18"/>
-      <c r="D28" s="18"/>
-      <c r="E28" s="18"/>
-      <c r="F28" s="18"/>
-      <c r="G28" s="18"/>
+      <c r="F26" s="19"/>
+      <c r="G26" s="16" t="str">
+        <f aca="false">IF(F26="","",IF(UPPER(TRIM(F26))="A","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="78.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="B27" s="7"/>
+      <c r="C27" s="7"/>
+      <c r="D27" s="7"/>
+      <c r="E27" s="7"/>
+      <c r="F27" s="19"/>
+      <c r="G27" s="16" t="str">
+        <f aca="false">IF(F27="","",IF(UPPER(TRIM(F27))="B","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="B28" s="7"/>
+      <c r="C28" s="7"/>
+      <c r="D28" s="7"/>
+      <c r="E28" s="7"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="18"/>
-      <c r="B29" s="18"/>
-      <c r="C29" s="18"/>
-      <c r="D29" s="18"/>
-      <c r="E29" s="18"/>
-      <c r="F29" s="18"/>
-      <c r="G29" s="18"/>
-    </row>
-    <row r="31" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="B31" s="6"/>
-      <c r="C31" s="6"/>
-      <c r="D31" s="6"/>
-      <c r="E31" s="6"/>
-      <c r="F31" s="6"/>
-      <c r="G31" s="6"/>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="B32" s="6"/>
-      <c r="C32" s="6"/>
-      <c r="D32" s="6"/>
-      <c r="E32" s="6"/>
-      <c r="F32" s="6"/>
-      <c r="G32" s="6"/>
+      <c r="A29" s="20"/>
+      <c r="B29" s="20"/>
+      <c r="C29" s="20"/>
+      <c r="D29" s="20"/>
+      <c r="E29" s="20"/>
+      <c r="F29" s="20"/>
+      <c r="G29" s="20"/>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="20"/>
+      <c r="B30" s="20"/>
+      <c r="C30" s="20"/>
+      <c r="D30" s="20"/>
+      <c r="E30" s="20"/>
+      <c r="F30" s="20"/>
+      <c r="G30" s="20"/>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="20"/>
+      <c r="B31" s="20"/>
+      <c r="C31" s="20"/>
+      <c r="D31" s="20"/>
+      <c r="E31" s="20"/>
+      <c r="F31" s="20"/>
+      <c r="G31" s="20"/>
+    </row>
+    <row r="32" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="B32" s="18" t="s">
+        <v>92</v>
+      </c>
+      <c r="C32" s="18"/>
+      <c r="D32" s="18"/>
+      <c r="E32" s="18"/>
+      <c r="F32" s="18"/>
+      <c r="G32" s="18"/>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="21" t="s">
+        <v>56</v>
+      </c>
+      <c r="B35" s="21"/>
+      <c r="C35" s="21"/>
+      <c r="D35" s="21"/>
+      <c r="E35" s="21"/>
+      <c r="F35" s="21"/>
+      <c r="G35" s="21"/>
+    </row>
+    <row r="36" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="22" t="s">
+        <v>93</v>
+      </c>
+      <c r="B36" s="23" t="s">
+        <v>94</v>
+      </c>
+      <c r="C36" s="23"/>
+      <c r="D36" s="23"/>
+      <c r="E36" s="23"/>
+      <c r="F36" s="23"/>
+      <c r="G36" s="23"/>
+    </row>
+    <row r="37" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="22" t="s">
+        <v>95</v>
+      </c>
+      <c r="B37" s="23" t="s">
+        <v>96</v>
+      </c>
+      <c r="C37" s="23"/>
+      <c r="D37" s="23"/>
+      <c r="E37" s="23"/>
+      <c r="F37" s="23"/>
+      <c r="G37" s="23"/>
+    </row>
+    <row r="39" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="B39" s="6"/>
+      <c r="C39" s="6"/>
+      <c r="D39" s="6"/>
+      <c r="E39" s="6"/>
+      <c r="F39" s="6"/>
+      <c r="G39" s="6"/>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="B40" s="6"/>
+      <c r="C40" s="6"/>
+      <c r="D40" s="6"/>
+      <c r="E40" s="6"/>
+      <c r="F40" s="6"/>
+      <c r="G40" s="6"/>
     </row>
   </sheetData>
-  <mergeCells count="24">
+  <mergeCells count="29">
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="B7:G7"/>
@@ -1719,8 +1982,7 @@
     <mergeCell ref="B14:G14"/>
     <mergeCell ref="A16:E16"/>
     <mergeCell ref="A17:E17"/>
-    <mergeCell ref="A18:E18"/>
-    <mergeCell ref="A19:E19"/>
+    <mergeCell ref="B18:G18"/>
     <mergeCell ref="A20:E20"/>
     <mergeCell ref="A21:E21"/>
     <mergeCell ref="A22:E22"/>
@@ -1728,9 +1990,15 @@
     <mergeCell ref="A24:E24"/>
     <mergeCell ref="A25:E25"/>
     <mergeCell ref="A26:E26"/>
-    <mergeCell ref="A27:G29"/>
-    <mergeCell ref="A31:G31"/>
-    <mergeCell ref="A32:G32"/>
+    <mergeCell ref="A27:E27"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="A29:G31"/>
+    <mergeCell ref="B32:G32"/>
+    <mergeCell ref="A35:G35"/>
+    <mergeCell ref="B36:G36"/>
+    <mergeCell ref="B37:G37"/>
+    <mergeCell ref="A39:G39"/>
+    <mergeCell ref="A40:G40"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -1747,7 +2015,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
@@ -1758,7 +2026,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>84</v>
+        <v>98</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1768,7 +2036,7 @@
     </row>
     <row r="4" customFormat="false" ht="78.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
@@ -1779,7 +2047,7 @@
     </row>
     <row r="5" customFormat="false" ht="78.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>86</v>
+        <v>100</v>
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
@@ -1790,66 +2058,66 @@
     </row>
     <row r="7" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>87</v>
+        <v>101</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>88</v>
+        <v>102</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="10" t="s">
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="12" t="s">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="10" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>94</v>
+        <v>108</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="12" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="10" t="s">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="12" t="s">
-        <v>99</v>
+        <v>113</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>100</v>
+        <v>114</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="10" t="s">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>102</v>
+        <v>116</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1880,7 +2148,7 @@
     </row>
     <row r="18" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="s">
-        <v>103</v>
+        <v>117</v>
       </c>
       <c r="B18" s="7"/>
       <c r="C18" s="7"/>
@@ -1889,13 +2157,13 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="s">
-        <v>104</v>
+        <v>118</v>
       </c>
       <c r="B19" s="7"/>
       <c r="C19" s="7"/>
       <c r="D19" s="7"/>
       <c r="E19" s="7"/>
-      <c r="F19" s="17"/>
+      <c r="F19" s="19"/>
       <c r="G19" s="16" t="str">
         <f aca="false">IF(F19="","",IF(UPPER(TRIM(F19))="JA","Riktig","Prøv igjen"))</f>
         <v/>
@@ -1903,13 +2171,13 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="7" t="s">
-        <v>105</v>
+        <v>119</v>
       </c>
       <c r="B20" s="7"/>
       <c r="C20" s="7"/>
       <c r="D20" s="7"/>
       <c r="E20" s="7"/>
-      <c r="F20" s="17"/>
+      <c r="F20" s="19"/>
       <c r="G20" s="16" t="str">
         <f aca="false">IF(F20="","",IF(UPPER(TRIM(F20))="NEI","Riktig","Prøv igjen"))</f>
         <v/>
@@ -1917,13 +2185,13 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="7" t="s">
-        <v>106</v>
+        <v>120</v>
       </c>
       <c r="B21" s="7"/>
       <c r="C21" s="7"/>
       <c r="D21" s="7"/>
       <c r="E21" s="7"/>
-      <c r="F21" s="17"/>
+      <c r="F21" s="19"/>
       <c r="G21" s="16" t="str">
         <f aca="false">IF(F21="","",IF(UPPER(TRIM(F21))="NEI","Riktig","Prøv igjen"))</f>
         <v/>
@@ -1931,13 +2199,13 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="7" t="s">
-        <v>107</v>
+        <v>121</v>
       </c>
       <c r="B22" s="7"/>
       <c r="C22" s="7"/>
       <c r="D22" s="7"/>
       <c r="E22" s="7"/>
-      <c r="F22" s="17"/>
+      <c r="F22" s="19"/>
       <c r="G22" s="16" t="str">
         <f aca="false">IF(F22="","",IF(UPPER(TRIM(F22))="NEI","Riktig","Prøv igjen"))</f>
         <v/>
@@ -1945,13 +2213,13 @@
     </row>
     <row r="23" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="7" t="s">
-        <v>108</v>
+        <v>122</v>
       </c>
       <c r="B23" s="7"/>
       <c r="C23" s="7"/>
       <c r="D23" s="7"/>
       <c r="E23" s="7"/>
-      <c r="F23" s="17"/>
+      <c r="F23" s="19"/>
       <c r="G23" s="16" t="str">
         <f aca="false">IF(F23="","",IF(UPPER(TRIM(F23))="B","Riktig","Prøv igjen"))</f>
         <v/>
@@ -1959,13 +2227,13 @@
     </row>
     <row r="24" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="7" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="B24" s="7"/>
       <c r="C24" s="7"/>
       <c r="D24" s="7"/>
       <c r="E24" s="7"/>
-      <c r="F24" s="17"/>
+      <c r="F24" s="19"/>
       <c r="G24" s="16" t="str">
         <f aca="false">IF(F24="","",IF(UPPER(TRIM(F24))="A","Riktig","Prøv igjen"))</f>
         <v/>
@@ -1973,13 +2241,13 @@
     </row>
     <row r="25" customFormat="false" ht="78.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="7" t="s">
-        <v>110</v>
+        <v>124</v>
       </c>
       <c r="B25" s="7"/>
       <c r="C25" s="7"/>
       <c r="D25" s="7"/>
       <c r="E25" s="7"/>
-      <c r="F25" s="17"/>
+      <c r="F25" s="19"/>
       <c r="G25" s="16" t="str">
         <f aca="false">IF(F25="","",IF(UPPER(TRIM(F25))="C","Riktig","Prøv igjen"))</f>
         <v/>
@@ -1987,7 +2255,7 @@
     </row>
     <row r="26" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="7" t="s">
-        <v>111</v>
+        <v>125</v>
       </c>
       <c r="B26" s="7"/>
       <c r="C26" s="7"/>
@@ -1995,56 +2263,106 @@
       <c r="E26" s="7"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="18"/>
-      <c r="B27" s="18"/>
-      <c r="C27" s="18"/>
-      <c r="D27" s="18"/>
-      <c r="E27" s="18"/>
-      <c r="F27" s="18"/>
-      <c r="G27" s="18"/>
+      <c r="A27" s="20"/>
+      <c r="B27" s="20"/>
+      <c r="C27" s="20"/>
+      <c r="D27" s="20"/>
+      <c r="E27" s="20"/>
+      <c r="F27" s="20"/>
+      <c r="G27" s="20"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="18"/>
-      <c r="B28" s="18"/>
-      <c r="C28" s="18"/>
-      <c r="D28" s="18"/>
-      <c r="E28" s="18"/>
-      <c r="F28" s="18"/>
-      <c r="G28" s="18"/>
+      <c r="A28" s="20"/>
+      <c r="B28" s="20"/>
+      <c r="C28" s="20"/>
+      <c r="D28" s="20"/>
+      <c r="E28" s="20"/>
+      <c r="F28" s="20"/>
+      <c r="G28" s="20"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="18"/>
-      <c r="B29" s="18"/>
-      <c r="C29" s="18"/>
-      <c r="D29" s="18"/>
-      <c r="E29" s="18"/>
-      <c r="F29" s="18"/>
-      <c r="G29" s="18"/>
-    </row>
-    <row r="31" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="B31" s="6"/>
-      <c r="C31" s="6"/>
-      <c r="D31" s="6"/>
-      <c r="E31" s="6"/>
-      <c r="F31" s="6"/>
-      <c r="G31" s="6"/>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="B32" s="6"/>
-      <c r="C32" s="6"/>
-      <c r="D32" s="6"/>
-      <c r="E32" s="6"/>
-      <c r="F32" s="6"/>
-      <c r="G32" s="6"/>
+      <c r="A29" s="20"/>
+      <c r="B29" s="20"/>
+      <c r="C29" s="20"/>
+      <c r="D29" s="20"/>
+      <c r="E29" s="20"/>
+      <c r="F29" s="20"/>
+      <c r="G29" s="20"/>
+    </row>
+    <row r="30" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="B30" s="18" t="s">
+        <v>126</v>
+      </c>
+      <c r="C30" s="18"/>
+      <c r="D30" s="18"/>
+      <c r="E30" s="18"/>
+      <c r="F30" s="18"/>
+      <c r="G30" s="18"/>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="21" t="s">
+        <v>56</v>
+      </c>
+      <c r="B33" s="21"/>
+      <c r="C33" s="21"/>
+      <c r="D33" s="21"/>
+      <c r="E33" s="21"/>
+      <c r="F33" s="21"/>
+      <c r="G33" s="21"/>
+    </row>
+    <row r="34" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="22" t="s">
+        <v>127</v>
+      </c>
+      <c r="B34" s="23" t="s">
+        <v>128</v>
+      </c>
+      <c r="C34" s="23"/>
+      <c r="D34" s="23"/>
+      <c r="E34" s="23"/>
+      <c r="F34" s="23"/>
+      <c r="G34" s="23"/>
+    </row>
+    <row r="35" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="22" t="s">
+        <v>129</v>
+      </c>
+      <c r="B35" s="23" t="s">
+        <v>130</v>
+      </c>
+      <c r="C35" s="23"/>
+      <c r="D35" s="23"/>
+      <c r="E35" s="23"/>
+      <c r="F35" s="23"/>
+      <c r="G35" s="23"/>
+    </row>
+    <row r="37" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="B37" s="6"/>
+      <c r="C37" s="6"/>
+      <c r="D37" s="6"/>
+      <c r="E37" s="6"/>
+      <c r="F37" s="6"/>
+      <c r="G37" s="6"/>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="B38" s="6"/>
+      <c r="C38" s="6"/>
+      <c r="D38" s="6"/>
+      <c r="E38" s="6"/>
+      <c r="F38" s="6"/>
+      <c r="G38" s="6"/>
     </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="20">
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="A15:G15"/>
@@ -2059,8 +2377,12 @@
     <mergeCell ref="A25:E25"/>
     <mergeCell ref="A26:E26"/>
     <mergeCell ref="A27:G29"/>
-    <mergeCell ref="A31:G31"/>
-    <mergeCell ref="A32:G32"/>
+    <mergeCell ref="B30:G30"/>
+    <mergeCell ref="A33:G33"/>
+    <mergeCell ref="B34:G34"/>
+    <mergeCell ref="B35:G35"/>
+    <mergeCell ref="A37:G37"/>
+    <mergeCell ref="A38:G38"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -2077,7 +2399,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
@@ -2088,7 +2410,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>113</v>
+        <v>132</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2098,7 +2420,7 @@
     </row>
     <row r="4" customFormat="false" ht="78.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>114</v>
+        <v>133</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
@@ -2109,7 +2431,7 @@
     </row>
     <row r="5" customFormat="false" ht="78.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>115</v>
+        <v>134</v>
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
@@ -2120,10 +2442,10 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="C7" s="14"/>
       <c r="D7" s="14"/>
@@ -2132,11 +2454,11 @@
       <c r="G7" s="14"/>
     </row>
     <row r="8" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="19" t="s">
-        <v>116</v>
+      <c r="A8" s="24" t="s">
+        <v>135</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>117</v>
+        <v>136</v>
       </c>
       <c r="C8" s="7"/>
       <c r="D8" s="7"/>
@@ -2145,11 +2467,11 @@
       <c r="G8" s="7"/>
     </row>
     <row r="9" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="19" t="s">
-        <v>118</v>
+      <c r="A9" s="24" t="s">
+        <v>137</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>119</v>
+        <v>138</v>
       </c>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
@@ -2158,11 +2480,11 @@
       <c r="G9" s="7"/>
     </row>
     <row r="10" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="19" t="s">
-        <v>120</v>
+      <c r="A10" s="24" t="s">
+        <v>139</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>121</v>
+        <v>140</v>
       </c>
       <c r="C10" s="7"/>
       <c r="D10" s="7"/>
@@ -2171,11 +2493,11 @@
       <c r="G10" s="7"/>
     </row>
     <row r="11" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="19" t="s">
-        <v>122</v>
+      <c r="A11" s="24" t="s">
+        <v>141</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>123</v>
+        <v>142</v>
       </c>
       <c r="C11" s="7"/>
       <c r="D11" s="7"/>
@@ -2184,11 +2506,11 @@
       <c r="G11" s="7"/>
     </row>
     <row r="12" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="19" t="s">
-        <v>124</v>
+      <c r="A12" s="24" t="s">
+        <v>143</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>125</v>
+        <v>144</v>
       </c>
       <c r="C12" s="7"/>
       <c r="D12" s="7"/>
@@ -2197,11 +2519,11 @@
       <c r="G12" s="7"/>
     </row>
     <row r="13" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="19" t="s">
-        <v>126</v>
+      <c r="A13" s="24" t="s">
+        <v>145</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>127</v>
+        <v>146</v>
       </c>
       <c r="C13" s="7"/>
       <c r="D13" s="7"/>
@@ -2226,7 +2548,7 @@
     </row>
     <row r="16" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="7" t="s">
-        <v>128</v>
+        <v>147</v>
       </c>
       <c r="B16" s="7"/>
       <c r="C16" s="7"/>
@@ -2235,13 +2557,13 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="7" t="s">
-        <v>129</v>
+        <v>148</v>
       </c>
       <c r="B17" s="7"/>
       <c r="C17" s="7"/>
       <c r="D17" s="7"/>
       <c r="E17" s="7"/>
-      <c r="F17" s="17"/>
+      <c r="F17" s="19"/>
       <c r="G17" s="16" t="str">
         <f aca="false">IF(F17="","",IF(UPPER(TRIM(F17))="JA","Riktig","Prøv igjen"))</f>
         <v/>
@@ -2249,13 +2571,13 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="s">
-        <v>130</v>
+        <v>149</v>
       </c>
       <c r="B18" s="7"/>
       <c r="C18" s="7"/>
       <c r="D18" s="7"/>
       <c r="E18" s="7"/>
-      <c r="F18" s="17"/>
+      <c r="F18" s="19"/>
       <c r="G18" s="16" t="str">
         <f aca="false">IF(F18="","",IF(UPPER(TRIM(F18))="JA","Riktig","Prøv igjen"))</f>
         <v/>
@@ -2263,13 +2585,13 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="s">
-        <v>131</v>
+        <v>150</v>
       </c>
       <c r="B19" s="7"/>
       <c r="C19" s="7"/>
       <c r="D19" s="7"/>
       <c r="E19" s="7"/>
-      <c r="F19" s="17"/>
+      <c r="F19" s="19"/>
       <c r="G19" s="16" t="str">
         <f aca="false">IF(F19="","",IF(UPPER(TRIM(F19))="JA","Riktig","Prøv igjen"))</f>
         <v/>
@@ -2277,13 +2599,13 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="7" t="s">
-        <v>132</v>
+        <v>151</v>
       </c>
       <c r="B20" s="7"/>
       <c r="C20" s="7"/>
       <c r="D20" s="7"/>
       <c r="E20" s="7"/>
-      <c r="F20" s="17"/>
+      <c r="F20" s="19"/>
       <c r="G20" s="16" t="str">
         <f aca="false">IF(F20="","",IF(UPPER(TRIM(F20))="NEI","Riktig","Prøv igjen"))</f>
         <v/>
@@ -2291,13 +2613,13 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="7" t="s">
-        <v>133</v>
+        <v>152</v>
       </c>
       <c r="B21" s="7"/>
       <c r="C21" s="7"/>
       <c r="D21" s="7"/>
       <c r="E21" s="7"/>
-      <c r="F21" s="17"/>
+      <c r="F21" s="19"/>
       <c r="G21" s="16" t="str">
         <f aca="false">IF(F21="","",IF(UPPER(TRIM(F21))="NEI","Riktig","Prøv igjen"))</f>
         <v/>
@@ -2305,13 +2627,13 @@
     </row>
     <row r="22" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="7" t="s">
-        <v>134</v>
+        <v>153</v>
       </c>
       <c r="B22" s="7"/>
       <c r="C22" s="7"/>
       <c r="D22" s="7"/>
       <c r="E22" s="7"/>
-      <c r="F22" s="17"/>
+      <c r="F22" s="19"/>
       <c r="G22" s="16" t="str">
         <f aca="false">IF(F22="","",IF(UPPER(TRIM(F22))="B","Riktig","Prøv igjen"))</f>
         <v/>
@@ -2319,13 +2641,13 @@
     </row>
     <row r="23" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="7" t="s">
-        <v>135</v>
+        <v>154</v>
       </c>
       <c r="B23" s="7"/>
       <c r="C23" s="7"/>
       <c r="D23" s="7"/>
       <c r="E23" s="7"/>
-      <c r="F23" s="17"/>
+      <c r="F23" s="19"/>
       <c r="G23" s="16" t="str">
         <f aca="false">IF(F23="","",IF(UPPER(TRIM(F23))="B","Riktig","Prøv igjen"))</f>
         <v/>
@@ -2333,13 +2655,13 @@
     </row>
     <row r="24" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="7" t="s">
-        <v>136</v>
+        <v>155</v>
       </c>
       <c r="B24" s="7"/>
       <c r="C24" s="7"/>
       <c r="D24" s="7"/>
       <c r="E24" s="7"/>
-      <c r="F24" s="17"/>
+      <c r="F24" s="19"/>
       <c r="G24" s="16" t="str">
         <f aca="false">IF(F24="","",IF(UPPER(TRIM(F24))="C","Riktig","Prøv igjen"))</f>
         <v/>
@@ -2347,7 +2669,7 @@
     </row>
     <row r="25" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="7" t="s">
-        <v>137</v>
+        <v>156</v>
       </c>
       <c r="B25" s="7"/>
       <c r="C25" s="7"/>
@@ -2355,56 +2677,106 @@
       <c r="E25" s="7"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="18"/>
-      <c r="B26" s="18"/>
-      <c r="C26" s="18"/>
-      <c r="D26" s="18"/>
-      <c r="E26" s="18"/>
-      <c r="F26" s="18"/>
-      <c r="G26" s="18"/>
+      <c r="A26" s="20"/>
+      <c r="B26" s="20"/>
+      <c r="C26" s="20"/>
+      <c r="D26" s="20"/>
+      <c r="E26" s="20"/>
+      <c r="F26" s="20"/>
+      <c r="G26" s="20"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="18"/>
-      <c r="B27" s="18"/>
-      <c r="C27" s="18"/>
-      <c r="D27" s="18"/>
-      <c r="E27" s="18"/>
-      <c r="F27" s="18"/>
-      <c r="G27" s="18"/>
+      <c r="A27" s="20"/>
+      <c r="B27" s="20"/>
+      <c r="C27" s="20"/>
+      <c r="D27" s="20"/>
+      <c r="E27" s="20"/>
+      <c r="F27" s="20"/>
+      <c r="G27" s="20"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="18"/>
-      <c r="B28" s="18"/>
-      <c r="C28" s="18"/>
-      <c r="D28" s="18"/>
-      <c r="E28" s="18"/>
-      <c r="F28" s="18"/>
-      <c r="G28" s="18"/>
-    </row>
-    <row r="30" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="6" t="s">
-        <v>138</v>
-      </c>
-      <c r="B30" s="6"/>
-      <c r="C30" s="6"/>
-      <c r="D30" s="6"/>
-      <c r="E30" s="6"/>
-      <c r="F30" s="6"/>
-      <c r="G30" s="6"/>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="B31" s="6"/>
-      <c r="C31" s="6"/>
-      <c r="D31" s="6"/>
-      <c r="E31" s="6"/>
-      <c r="F31" s="6"/>
-      <c r="G31" s="6"/>
+      <c r="A28" s="20"/>
+      <c r="B28" s="20"/>
+      <c r="C28" s="20"/>
+      <c r="D28" s="20"/>
+      <c r="E28" s="20"/>
+      <c r="F28" s="20"/>
+      <c r="G28" s="20"/>
+    </row>
+    <row r="29" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="B29" s="18" t="s">
+        <v>157</v>
+      </c>
+      <c r="C29" s="18"/>
+      <c r="D29" s="18"/>
+      <c r="E29" s="18"/>
+      <c r="F29" s="18"/>
+      <c r="G29" s="18"/>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="21" t="s">
+        <v>56</v>
+      </c>
+      <c r="B32" s="21"/>
+      <c r="C32" s="21"/>
+      <c r="D32" s="21"/>
+      <c r="E32" s="21"/>
+      <c r="F32" s="21"/>
+      <c r="G32" s="21"/>
+    </row>
+    <row r="33" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="22" t="s">
+        <v>158</v>
+      </c>
+      <c r="B33" s="23" t="s">
+        <v>159</v>
+      </c>
+      <c r="C33" s="23"/>
+      <c r="D33" s="23"/>
+      <c r="E33" s="23"/>
+      <c r="F33" s="23"/>
+      <c r="G33" s="23"/>
+    </row>
+    <row r="34" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="22" t="s">
+        <v>160</v>
+      </c>
+      <c r="B34" s="23" t="s">
+        <v>161</v>
+      </c>
+      <c r="C34" s="23"/>
+      <c r="D34" s="23"/>
+      <c r="E34" s="23"/>
+      <c r="F34" s="23"/>
+      <c r="G34" s="23"/>
+    </row>
+    <row r="36" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="B36" s="6"/>
+      <c r="C36" s="6"/>
+      <c r="D36" s="6"/>
+      <c r="E36" s="6"/>
+      <c r="F36" s="6"/>
+      <c r="G36" s="6"/>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="B37" s="6"/>
+      <c r="C37" s="6"/>
+      <c r="D37" s="6"/>
+      <c r="E37" s="6"/>
+      <c r="F37" s="6"/>
+      <c r="G37" s="6"/>
     </row>
   </sheetData>
-  <mergeCells count="23">
+  <mergeCells count="27">
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="B7:G7"/>
@@ -2426,8 +2798,12 @@
     <mergeCell ref="A24:E24"/>
     <mergeCell ref="A25:E25"/>
     <mergeCell ref="A26:G28"/>
-    <mergeCell ref="A30:G30"/>
-    <mergeCell ref="A31:G31"/>
+    <mergeCell ref="B29:G29"/>
+    <mergeCell ref="A32:G32"/>
+    <mergeCell ref="B33:G33"/>
+    <mergeCell ref="B34:G34"/>
+    <mergeCell ref="A36:G36"/>
+    <mergeCell ref="A37:G37"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/pensum/ol11/OL11_Klasseoppgaver_v5.xlsx
+++ b/pensum/ol11/OL11_Klasseoppgaver_v5.xlsx
@@ -266,13 +266,13 @@
     <t xml:space="preserve">Mulige forbindelser</t>
   </si>
   <si>
-    <t xml:space="preserve">n × (n − 1) / 2, der n er antall personer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">a)  Med tre personer er det 3 mulige forbindelser. Hvor mange blir det når Fjell er fem personer? Bruk n × (n − 1) / 2.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">n × (n − 1) / 2 er en telleregel for antall mulige forbindelser mellom to personer, ikke en formel i boka. Den brukes til å vise hvorfor arbeidsdeling og samordning må bestemmes (definisjonen i kap. 12).</t>
+    <t xml:space="preserve">antall personer × (antall personer − 1) / 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">a)  Med tre personer er det 3 mulige forbindelser. Hvor mange blir det når Fjell er fem personer? Bruk antall personer × (antall personer − 1) / 2.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mulige forbindelser = antall personer × (antall personer − 1) / 2. Det er en telleregel for antall mulige forbindelser mellom to personer, ikke en formel i boka. Den brukes til å vise hvorfor arbeidsdeling og samordning må bestemmes (definisjonen i kap. 12).</t>
   </si>
   <si>
     <t xml:space="preserve">b)  Hvilke av disse trekkene ved Fjell er formelle, etter bokas kjennetegn? Svar ja eller nei for hvert, og si hvilket kjennetegn de formelle hører til.</t>

--- a/pensum/ol11/OL11_Klasseoppgaver_v5.xlsx
+++ b/pensum/ol11/OL11_Klasseoppgaver_v5.xlsx
@@ -26,7 +26,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="163">
   <si>
-    <t xml:space="preserve">Klasseoppgaver til Organisasjon og ledelse kapittel 11: Hva er en organisasjon? (V5)</t>
+    <t xml:space="preserve">Klasseoppgaver til Organisasjon og ledelse kapittel 11: Hva er en organisasjon? (versjon 5)</t>
   </si>
   <si>
     <t xml:space="preserve">LØM · Fagskolen Oslo, Avdeling Elkraft · versjon 5, oktober 2026</t>

--- a/pensum/ol11/OL11_Klasseoppgaver_v5.xlsx
+++ b/pensum/ol11/OL11_Klasseoppgaver_v5.xlsx
@@ -269,7 +269,7 @@
     <t xml:space="preserve">antall personer × (antall personer − 1) / 2</t>
   </si>
   <si>
-    <t xml:space="preserve">a)  Med tre personer er det 3 mulige forbindelser. Hvor mange blir det når Fjell er fem personer? Bruk antall personer × (antall personer − 1) / 2.</t>
+    <t xml:space="preserve">a)  Med tre personer er det 3 × 2 / 2 = 3 mulige forbindelser. Hvor mange blir det når Fjell er fem personer? Bruk antall personer × (antall personer − 1) / 2.</t>
   </si>
   <si>
     <t xml:space="preserve">Mulige forbindelser = antall personer × (antall personer − 1) / 2. Det er en telleregel for antall mulige forbindelser mellom to personer, ikke en formel i boka. Den brukes til å vise hvorfor arbeidsdeling og samordning må bestemmes (definisjonen i kap. 12).</t>
